--- a/data/trans_orig/IP25A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27011</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>40931</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35300</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52462</t>
+          <t>52637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72424</t>
+          <t>71931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>43517</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>58305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54906</t>
+          <t>55059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>88826</t>
+          <t>89319</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108788</t>
+          <t>108613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,36%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137591</t>
+          <t>137701</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168678</t>
+          <t>170856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154434</t>
+          <t>154945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187022</t>
+          <t>186015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303304</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>346718</t>
+          <t>344483</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210173</t>
+          <t>207995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>241260</t>
+          <t>241150</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,48%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236336</t>
+          <t>237343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>268924</t>
+          <t>268413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455491</t>
+          <t>457726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498905</t>
+          <t>499821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>27745</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44920</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34683</t>
+          <t>34097</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51194</t>
+          <t>51260</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66568</t>
+          <t>66524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91647</t>
+          <t>89509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>31,8%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105531</t>
+          <t>105957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>122503</t>
+          <t>122706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79869</t>
+          <t>79803</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96380</t>
+          <t>96966</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189867</t>
+          <t>192005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214946</t>
+          <t>214990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204283</t>
+          <t>203162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>241902</t>
+          <t>242286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222809</t>
+          <t>221905</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>259564</t>
+          <t>259910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>436658</t>
+          <t>434098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490585</t>
+          <t>492827</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371848</t>
+          <t>371464</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>409467</t>
+          <t>410588</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>371659</t>
+          <t>371313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>408414</t>
+          <t>409318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>754388</t>
+          <t>752146</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>808315</t>
+          <t>810875</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,13%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30020</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45353</t>
+          <t>45344</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26219</t>
+          <t>27105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41698</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61560</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>83121</t>
+          <t>82713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,2%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41332</t>
+          <t>41341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56665</t>
+          <t>56485</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>39181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>54328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106558</t>
+          <t>106701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,47%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129078</t>
+          <t>127887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>159654</t>
+          <t>160704</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150917</t>
+          <t>151071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185106</t>
+          <t>184624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>288464</t>
+          <t>286177</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>332227</t>
+          <t>334780</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>236609</t>
+          <t>235559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>267185</t>
+          <t>268376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264958</t>
+          <t>265440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299147</t>
+          <t>298993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>514101</t>
+          <t>511548</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>557864</t>
+          <t>560151</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>34360</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52205</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37984</t>
+          <t>37367</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56832</t>
+          <t>56047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>76101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101446</t>
+          <t>104182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96850</t>
+          <t>95219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>114575</t>
+          <t>114695</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94071</t>
+          <t>94856</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112919</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>198512</t>
+          <t>195776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223836</t>
+          <t>223857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,63%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>205233</t>
+          <t>204560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>246614</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227357</t>
+          <t>227830</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>267792</t>
+          <t>268253</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>442283</t>
+          <t>445048</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>500724</t>
+          <t>502955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,26%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>385389</t>
+          <t>387354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>426770</t>
+          <t>427443</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,98%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>414608</t>
+          <t>414147</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>455043</t>
+          <t>454570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>813680</t>
+          <t>811449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>872121</t>
+          <t>869356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>31887</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40694</t>
+          <t>41028</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51540</t>
+          <t>51921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69315</t>
+          <t>69656</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19410</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31200</t>
+          <t>30987</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23139</t>
+          <t>22805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45816</t>
+          <t>45475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63591</t>
+          <t>63210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188955</t>
+          <t>189556</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>224324</t>
+          <t>222812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194795</t>
+          <t>193479</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>229476</t>
+          <t>228391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>393813</t>
+          <t>391850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>441121</t>
+          <t>442924</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198721</t>
+          <t>200233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>234090</t>
+          <t>233489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219736</t>
+          <t>220821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254417</t>
+          <t>255733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431136</t>
+          <t>429333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>478444</t>
+          <t>480407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>55,08%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57560</t>
+          <t>56950</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50390</t>
+          <t>50797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70326</t>
+          <t>71689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>93074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120559</t>
+          <t>122502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90470</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109668</t>
+          <t>109828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91685</t>
+          <t>90322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111621</t>
+          <t>111214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189482</t>
+          <t>187539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215881</t>
+          <t>216967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>259939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>300004</t>
+          <t>298730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>285822</t>
+          <t>284906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>329572</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>556494</t>
+          <t>559183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>617007</t>
+          <t>616350</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,51%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>322368</t>
+          <t>323642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>363717</t>
+          <t>362433</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346857</t>
+          <t>345484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>389234</t>
+          <t>390150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>680421</t>
+          <t>681078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>740934</t>
+          <t>738245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28324</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21714</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>35603</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,27%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>33732</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26143</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>40931</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>26319</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>40792</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>39,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28324</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>21743</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>35433</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>52124</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71931</t>
+          <t>73196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,39%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48478</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41199</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55088</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>63,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,73%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>50716</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43517</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>58305</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43656</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>58129</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>60,06%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>51,53%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>69,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>48478</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>41369</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55059</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>63,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89319</t>
+          <t>88054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>108613</t>
+          <t>109126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>76802</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76802</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76802</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>84448</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>84448</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>84448</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76802</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76802</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76802</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>170188</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>155109</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>186627</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40,2%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>44,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>153778</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>137701</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>170856</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>138924</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>170616</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>40,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>36,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,1%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>170188</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>154945</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>186015</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>40,2%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>302388</t>
+          <t>300894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>344483</t>
+          <t>345666</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,09%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>385</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>253170</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>236731</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>268249</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>59,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>55,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>342</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>225073</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>207995</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>241150</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>208235</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>239927</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>59,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>385</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>253170</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>237343</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>268413</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>59,8%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>457726</t>
+          <t>456543</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>499821</t>
+          <t>501315</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>423358</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>423358</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>423358</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>570</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>378851</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>378851</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>378851</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>423358</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>423358</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>423358</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42960</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34919</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>50917</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,64%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>38,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>35555</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27745</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44494</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27383</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44606</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>23,63%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>42960</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>34097</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51260</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66524</t>
+          <t>65230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89509</t>
+          <t>90675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>88103</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>80146</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>96144</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>67,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>61,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>114896</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>105957</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>122706</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>105845</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>123068</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>76,37%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>88103</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>79803</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>96966</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>67,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>192005</t>
+          <t>190839</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214990</t>
+          <t>216284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>131063</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>131063</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>131063</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150451</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150451</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150451</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>131063</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>131063</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>131063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>241471</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>222024</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>260918</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>41,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>223065</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>203162</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>242286</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>203647</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>241490</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>36,34%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>241471</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>221905</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>259910</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>434098</t>
+          <t>435683</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>492827</t>
+          <t>492189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>389752</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>370305</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>409199</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>58,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>64,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>390685</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>371464</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>410588</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>372260</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>410103</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>63,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>66,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>389752</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>371313</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>409318</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>752146</t>
+          <t>752784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>810875</t>
+          <t>809290</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>631223</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>631223</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>631223</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>613750</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>613750</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>631223</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>631223</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>631223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2140,13 +2140,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,72 +2325,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34355</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26904</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42009</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>42,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,04%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>37715</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>30200</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45344</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>31115</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>45746</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34355</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27105</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>42252</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>42,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61417</t>
+          <t>61796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82713</t>
+          <t>83340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -2438,72 +2438,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47078</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39424</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54529</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>57,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>48,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>66,96%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48970</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41341</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56485</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40939</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55570</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>56,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,69%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>47078</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>39181</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>54328</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>57,81%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85405</t>
+          <t>84778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>106322</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,24%</t>
         </is>
       </c>
     </row>
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>86685</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>86685</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>86685</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>81433</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>81433</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>81433</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>167560</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>149194</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>184117</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,91%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>143692</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>127887</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>160704</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>128327</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>160217</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>36,26%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>167560</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>151071</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>184624</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286177</t>
+          <t>288914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>334780</t>
+          <t>335310</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>282504</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>265947</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>300870</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>66,85%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>367</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>252571</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>235559</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>268376</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>236046</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>267936</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>63,74%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>282504</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>265440</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>298993</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>62,77%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>511548</t>
+          <t>511018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>560151</t>
+          <t>557414</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,86%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>450064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>450064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>450064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>572</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>396263</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>396263</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>396263</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>450064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>450064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>450064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,72 +3011,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46314</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>37143</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55689</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>42991</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34360</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53836</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34085</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>52381</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>28,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>46314</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>37367</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>56047</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76101</t>
+          <t>77054</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104182</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -3124,72 +3124,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>104589</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95214</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>113760</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>63,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>75,39%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>106064</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>95219</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>114695</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>96674</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>114970</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>71,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,95%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>104589</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>94856</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>113536</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>69,31%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>195776</t>
+          <t>196072</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>223857</t>
+          <t>222904</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>150903</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>150903</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>150903</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>149055</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>149055</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>149055</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>150903</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>150903</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>150903</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>248229</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>227427</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>269734</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>224398</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>204560</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>244649</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>204349</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>246544</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,51%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,37%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>38,71%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>248229</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>227830</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>268253</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>36,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>445048</t>
+          <t>443396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>502955</t>
+          <t>501711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>434171</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>412666</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>454973</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>591</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>407605</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>387354</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>427443</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>385459</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>427654</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,49%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>61,29%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>620</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>434171</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>414147</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>454570</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>63,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>811449</t>
+          <t>812693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>869356</t>
+          <t>871008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>682400</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>682400</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>682400</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>632003</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>632003</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>632003</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>682400</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>682400</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>682400</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3743,13 +3743,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,72 +3928,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34125</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27156</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40722</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,46%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26202</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20310</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31887</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20299</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>32014</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>51,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34125</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27464</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41028</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>51885</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69656</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29708</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>23111</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36677</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>46,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>36,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25095</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19410</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30987</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19283</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>30998</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>48,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60,41%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>29708</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22805</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36369</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>46,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45475</t>
+          <t>45542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63210</t>
+          <t>63246</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>63833</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>63833</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>63833</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>51297</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>51297</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>51297</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>63833</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>63833</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>63833</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>212150</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>194447</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>230940</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>47,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>306</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>206042</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>189556</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>222812</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>188681</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>221208</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>48,7%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>44,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,67%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>212150</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>193479</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>228391</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>391850</t>
+          <t>393951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442924</t>
+          <t>442353</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,71%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>237062</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218272</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>254765</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>217003</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200233</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>233489</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>201837</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>234364</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>51,3%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>47,33%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>55,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>237062</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>220821</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>255733</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>429333</t>
+          <t>429904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>480407</t>
+          <t>478306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>449212</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>449212</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>449212</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>423045</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>423045</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>423045</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>449212</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>449212</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>449212</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,72 +4614,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>60787</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51349</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>72506</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>46791</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38202</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56950</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>37208</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>55598</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>60787</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>50797</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>71689</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,52%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93074</t>
+          <t>93577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122502</t>
+          <t>121361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -4727,72 +4727,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>101224</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89505</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>110662</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>62,48%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>101239</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>91080</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>109828</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>92432</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>110822</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>68,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>101224</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>90322</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>111214</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>62,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>187539</t>
+          <t>188680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>216967</t>
+          <t>216464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>162011</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>162011</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>162011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148030</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148030</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148030</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>162011</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>162011</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>162011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,72 +4957,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>307063</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>285940</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>329699</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>45,49%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>42,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,84%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>412</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>279034</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>259939</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>298730</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>260763</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>300181</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>44,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>48,0%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>307063</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>284906</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>329572</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>45,49%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>559183</t>
+          <t>558745</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>616350</t>
+          <t>613965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>530</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>367993</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>345357</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>389116</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>54,51%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,16%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>57,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>343338</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>323642</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>362433</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>322191</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>361609</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>55,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>52,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>58,23%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>367993</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>345484</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>390150</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>54,51%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>681078</t>
+          <t>683463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>738245</t>
+          <t>738683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>675056</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>622372</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>622372</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>622372</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>675056</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
